--- a/public/samples/community-donors-sample.xlsx
+++ b/public/samples/community-donors-sample.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,6 +410,9 @@
         <v>blood_group</v>
       </c>
       <c r="D1" t="str">
+        <v>gender</v>
+      </c>
+      <c r="E1" t="str">
         <v>Address</v>
       </c>
     </row>
@@ -424,6 +427,9 @@
         <v>O+</v>
       </c>
       <c r="D2" t="str">
+        <v>male</v>
+      </c>
+      <c r="E2" t="str">
         <v>মিরপুর-১০</v>
       </c>
     </row>
@@ -438,6 +444,9 @@
         <v>A+</v>
       </c>
       <c r="D3" t="str">
+        <v>female</v>
+      </c>
+      <c r="E3" t="str">
         <v>গুলশান-২</v>
       </c>
     </row>
@@ -452,6 +461,9 @@
         <v>B+</v>
       </c>
       <c r="D4" t="str">
+        <v>male</v>
+      </c>
+      <c r="E4" t="str">
         <v>আগ্রাবাদ</v>
       </c>
     </row>
@@ -466,6 +478,9 @@
         <v>AB+</v>
       </c>
       <c r="D5" t="str">
+        <v>male</v>
+      </c>
+      <c r="E5" t="str">
         <v>জিন্দাবাজার</v>
       </c>
     </row>
@@ -480,6 +495,9 @@
         <v>O-</v>
       </c>
       <c r="D6" t="str">
+        <v>female</v>
+      </c>
+      <c r="E6" t="str">
         <v>শাহ মখদুম</v>
       </c>
     </row>
@@ -494,6 +512,9 @@
         <v>A-</v>
       </c>
       <c r="D7" t="str">
+        <v>male</v>
+      </c>
+      <c r="E7" t="str">
         <v>ধানমন্ডি ৩২</v>
       </c>
     </row>
@@ -508,6 +529,9 @@
         <v>B-</v>
       </c>
       <c r="D8" t="str">
+        <v>female</v>
+      </c>
+      <c r="E8" t="str">
         <v>উত্তরা সেক্টর ৭</v>
       </c>
     </row>
@@ -522,6 +546,9 @@
         <v>AB-</v>
       </c>
       <c r="D9" t="str">
+        <v>male</v>
+      </c>
+      <c r="E9" t="str">
         <v>মগবাজার</v>
       </c>
     </row>
@@ -536,6 +563,9 @@
         <v>O+</v>
       </c>
       <c r="D10" t="str">
+        <v>female</v>
+      </c>
+      <c r="E10" t="str">
         <v>বনানী</v>
       </c>
     </row>
@@ -550,12 +580,15 @@
         <v>A+</v>
       </c>
       <c r="D11" t="str">
+        <v>male</v>
+      </c>
+      <c r="E11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>